--- a/Morgan_etal_2014/Morgan_etal_2014_DataS1_snapshot.xlsx
+++ b/Morgan_etal_2014/Morgan_etal_2014_DataS1_snapshot.xlsx
@@ -5514,13 +5514,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C489A9-A3BE-4B9F-9A64-6B461BCD2F0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDFF97C2-9023-47AA-B14E-881B5A8A7EFC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA01E7C-F001-4C56-A925-EC5023C197B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43DD0A6A-321F-4340-BBF2-BDD869672663}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57CB2C1C-D6B5-4490-B8B4-78DA12681146}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A46945C3-47CB-4472-B169-E9599199527F}"/>
 </file>